--- a/notebooks/laparoscopy_cleaned.xlsx
+++ b/notebooks/laparoscopy_cleaned.xlsx
@@ -701,11 +701,7 @@
           <t>Dr Vaylann</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
@@ -720,7 +716,7 @@
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="b">
+      <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -818,11 +814,7 @@
           <t>Dr Lam</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
@@ -939,11 +931,7 @@
           <t>Dr Limbe</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
@@ -1056,11 +1044,7 @@
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1179,11 +1163,7 @@
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1198,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="b">
+      <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="inlineStr"/>
@@ -1310,11 +1290,7 @@
           <t>Dr Widmann</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1329,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="b">
+      <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -1448,7 +1424,7 @@
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="b">
+      <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -1573,7 +1549,7 @@
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="b">
+      <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -1685,11 +1661,7 @@
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1704,7 +1676,7 @@
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="b">
+      <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -1804,11 +1776,7 @@
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1935,7 +1903,7 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
+          <t>Dr. Madalitso</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -1952,7 +1920,7 @@
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="b">
+      <c r="AE12" t="n">
         <v>0</v>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -2058,11 +2026,7 @@
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
@@ -2189,11 +2153,7 @@
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
@@ -2208,7 +2168,7 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="b">
+      <c r="AE14" t="n">
         <v>0</v>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -2320,11 +2280,7 @@
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
@@ -2339,7 +2295,7 @@
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="b">
+      <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -2451,11 +2407,7 @@
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
@@ -2466,15 +2418,15 @@
         <v>112</v>
       </c>
       <c r="AB16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Inadvertent perforation of peritoneum</t>
+          <t>TEP to TAPP</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="b">
+      <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -2586,11 +2538,7 @@
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2605,7 +2553,7 @@
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="b">
+      <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -2715,11 +2663,7 @@
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2734,7 +2678,7 @@
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="b">
+      <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -2832,11 +2776,7 @@
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2961,11 +2901,7 @@
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2980,7 +2916,7 @@
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="b">
+      <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="inlineStr"/>
@@ -3078,11 +3014,7 @@
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
         <is>
@@ -3097,7 +3029,7 @@
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="b">
+      <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="inlineStr"/>
@@ -3205,11 +3137,7 @@
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
         <v>15</v>
@@ -3318,11 +3246,7 @@
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
         <v>15</v>
@@ -3447,7 +3371,7 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
+          <t>Dr. Madalitso</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3464,7 +3388,7 @@
       </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="b">
+      <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="inlineStr"/>
@@ -3722,7 +3646,7 @@
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="b">
+      <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="inlineStr"/>
@@ -3830,11 +3754,7 @@
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3853,7 +3773,7 @@
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="b">
+      <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="inlineStr"/>
@@ -3965,11 +3885,7 @@
           <t>Dr Widmann</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr">
         <is>
@@ -4094,11 +4010,7 @@
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr">
         <is>
@@ -4111,7 +4023,7 @@
       </c>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="b">
+      <c r="AE29" t="n">
         <v>0</v>
       </c>
       <c r="AF29" t="inlineStr"/>
@@ -4211,11 +4123,7 @@
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4336,11 +4244,7 @@
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr">
         <is>
@@ -4570,11 +4474,7 @@
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr">
         <is>
@@ -4589,7 +4489,7 @@
       </c>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="b">
+      <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="inlineStr"/>
@@ -4697,11 +4597,7 @@
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr">
         <is>
@@ -4716,7 +4612,7 @@
       </c>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="b">
+      <c r="AE34" t="n">
         <v>0</v>
       </c>
       <c r="AF34" t="inlineStr"/>
@@ -4828,11 +4724,7 @@
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
         <v>50</v>
@@ -4845,7 +4737,7 @@
       </c>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="b">
+      <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="inlineStr"/>
@@ -4953,11 +4845,7 @@
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4972,7 +4860,7 @@
       </c>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="b">
+      <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="inlineStr"/>
@@ -5088,11 +4976,7 @@
           <t>Dr Vaylann</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5107,7 +4991,7 @@
       </c>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="b">
+      <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="inlineStr"/>
@@ -5215,11 +5099,7 @@
         </is>
       </c>
       <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5344,11 +5224,7 @@
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5363,7 +5239,7 @@
       </c>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="b">
+      <c r="AE39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5475,11 +5351,7 @@
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
         <v>20</v>
@@ -5600,7 +5472,7 @@
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
+          <t>Dr. Madalitso</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5617,7 +5489,7 @@
       </c>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="b">
+      <c r="AE41" t="n">
         <v>0</v>
       </c>
       <c r="AF41" t="inlineStr"/>
@@ -5729,11 +5601,7 @@
         </is>
       </c>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
         <is>
@@ -5748,7 +5616,7 @@
       </c>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="b">
+      <c r="AE42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5856,11 +5724,7 @@
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
         <v>66</v>
@@ -5873,7 +5737,7 @@
       </c>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="b">
+      <c r="AE43" t="n">
         <v>0</v>
       </c>
       <c r="AF43" t="inlineStr"/>
@@ -5973,11 +5837,7 @@
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
         <v>90</v>
@@ -5990,7 +5850,7 @@
       </c>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="b">
+      <c r="AE44" t="n">
         <v>0</v>
       </c>
       <c r="AF44" t="inlineStr"/>
@@ -6102,11 +5962,7 @@
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6121,7 +5977,7 @@
       </c>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="b">
+      <c r="AE45" t="n">
         <v>0</v>
       </c>
       <c r="AF45" t="inlineStr"/>
@@ -6227,16 +6083,8 @@
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
         <v>95</v>
       </c>
@@ -6358,11 +6206,7 @@
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr">
         <is>
@@ -6383,7 +6227,7 @@
       <c r="AD47" t="n">
         <v>55</v>
       </c>
-      <c r="AE47" t="b">
+      <c r="AE47" t="n">
         <v>1</v>
       </c>
       <c r="AF47" t="inlineStr">
@@ -6503,11 +6347,7 @@
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr">
         <is>
@@ -6634,7 +6474,7 @@
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
+          <t>Dr. Madalitso</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -6651,7 +6491,7 @@
       </c>
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="b">
+      <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="inlineStr"/>
@@ -6759,11 +6599,7 @@
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
         <v>95</v>
@@ -6886,16 +6722,8 @@
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Dr Widmann</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Dr Madalitso</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr">
         <is>
           <t>&lt;10</t>
@@ -6909,7 +6737,7 @@
       </c>
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="b">
+      <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="inlineStr"/>
@@ -7021,11 +6849,7 @@
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
         <v>70</v>
@@ -7038,7 +6862,7 @@
       </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="b">
+      <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="inlineStr"/>
@@ -7261,11 +7085,7 @@
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr">
         <is>
@@ -7386,11 +7206,7 @@
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr">
         <is>
@@ -7517,7 +7333,7 @@
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
+          <t>Dr. Madalitso</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -7640,11 +7456,7 @@
         </is>
       </c>
       <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
         <v>90</v>
@@ -7765,11 +7577,7 @@
         </is>
       </c>
       <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr">
         <is>
@@ -7784,7 +7592,7 @@
       </c>
       <c r="AC58" t="inlineStr"/>
       <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="b">
+      <c r="AE58" t="n">
         <v>0</v>
       </c>
       <c r="AF58" t="inlineStr"/>
@@ -7896,11 +7704,7 @@
         </is>
       </c>
       <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr">
         <is>
@@ -7913,7 +7717,7 @@
       </c>
       <c r="AC59" t="inlineStr"/>
       <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="b">
+      <c r="AE59" t="n">
         <v>0</v>
       </c>
       <c r="AF59" t="inlineStr"/>
@@ -8027,7 +7831,7 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Dr James</t>
+          <t>Visiting Resident</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8154,7 +7958,7 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Dr James</t>
+          <t>Visiting Resident</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8171,7 +7975,7 @@
       </c>
       <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="b">
+      <c r="AE61" t="n">
         <v>0</v>
       </c>
       <c r="AF61" t="inlineStr"/>
@@ -8285,7 +8089,7 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Dr James</t>
+          <t>Visiting Resident</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -8410,11 +8214,7 @@
         </is>
       </c>
       <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr">
         <is>
@@ -8537,11 +8337,7 @@
         </is>
       </c>
       <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>Dr Widmann</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr">
         <is>
@@ -8666,11 +8462,7 @@
         </is>
       </c>
       <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr">
         <is>
@@ -8683,7 +8475,7 @@
       </c>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
-      <c r="AE65" t="b">
+      <c r="AE65" t="n">
         <v>0</v>
       </c>
       <c r="AF65" t="inlineStr"/>
@@ -8795,11 +8587,7 @@
         </is>
       </c>
       <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr">
         <is>
@@ -8814,7 +8602,7 @@
       </c>
       <c r="AC66" t="inlineStr"/>
       <c r="AD66" t="inlineStr"/>
-      <c r="AE66" t="b">
+      <c r="AE66" t="n">
         <v>0</v>
       </c>
       <c r="AF66" t="inlineStr"/>
@@ -8924,11 +8712,7 @@
         </is>
       </c>
       <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
+      <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr">
         <is>
@@ -9051,11 +8835,7 @@
         </is>
       </c>
       <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr">
         <is>
@@ -9070,7 +8850,7 @@
       </c>
       <c r="AC68" t="inlineStr"/>
       <c r="AD68" t="inlineStr"/>
-      <c r="AE68" t="b">
+      <c r="AE68" t="n">
         <v>0</v>
       </c>
       <c r="AF68" t="inlineStr"/>
@@ -9182,11 +8962,7 @@
         </is>
       </c>
       <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
         <v>90</v>
@@ -9199,7 +8975,7 @@
       </c>
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr"/>
-      <c r="AE69" t="b">
+      <c r="AE69" t="n">
         <v>0</v>
       </c>
       <c r="AF69" t="inlineStr"/>
@@ -9311,11 +9087,7 @@
         </is>
       </c>
       <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
         <v>30</v>
@@ -9328,7 +9100,7 @@
       </c>
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr"/>
-      <c r="AE70" t="b">
+      <c r="AE70" t="n">
         <v>0</v>
       </c>
       <c r="AF70" t="inlineStr"/>
@@ -9430,16 +9202,8 @@
         </is>
       </c>
       <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
         <v>85</v>
       </c>
@@ -9451,7 +9215,7 @@
       </c>
       <c r="AC71" t="inlineStr"/>
       <c r="AD71" t="inlineStr"/>
-      <c r="AE71" t="b">
+      <c r="AE71" t="n">
         <v>0</v>
       </c>
       <c r="AF71" t="inlineStr"/>
@@ -9553,14 +9317,10 @@
         </is>
       </c>
       <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>Dr Mumba</t>
+          <t>Dr Wongani</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -9576,7 +9336,7 @@
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
-      <c r="AE72" t="b">
+      <c r="AE72" t="n">
         <v>0</v>
       </c>
       <c r="AF72" t="inlineStr"/>
@@ -9680,11 +9440,7 @@
         </is>
       </c>
       <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
         <v>40</v>
@@ -9697,7 +9453,7 @@
       </c>
       <c r="AC73" t="inlineStr"/>
       <c r="AD73" t="inlineStr"/>
-      <c r="AE73" t="b">
+      <c r="AE73" t="n">
         <v>0</v>
       </c>
       <c r="AF73" t="inlineStr"/>
@@ -9809,11 +9565,7 @@
         </is>
       </c>
       <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr">
         <is>
@@ -9828,7 +9580,7 @@
       </c>
       <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="inlineStr"/>
-      <c r="AE74" t="b">
+      <c r="AE74" t="n">
         <v>0</v>
       </c>
       <c r="AF74" t="inlineStr"/>
@@ -9928,11 +9680,7 @@
         </is>
       </c>
       <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr">
         <is>
@@ -9945,7 +9693,7 @@
       </c>
       <c r="AC75" t="inlineStr"/>
       <c r="AD75" t="inlineStr"/>
-      <c r="AE75" t="b">
+      <c r="AE75" t="n">
         <v>0</v>
       </c>
       <c r="AF75" t="inlineStr"/>
@@ -10059,11 +9807,7 @@
           <t>Dr Beth</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Dr Vitu</t>
-        </is>
-      </c>
+      <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr">
         <is>
@@ -10076,7 +9820,7 @@
       </c>
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr"/>
-      <c r="AE76" t="b">
+      <c r="AE76" t="n">
         <v>0</v>
       </c>
       <c r="AF76" t="inlineStr"/>
@@ -10188,11 +9932,7 @@
         </is>
       </c>
       <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
+      <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr">
         <is>
@@ -10207,7 +9947,7 @@
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
-      <c r="AE77" t="b">
+      <c r="AE77" t="n">
         <v>0</v>
       </c>
       <c r="AF77" t="inlineStr"/>
@@ -10311,16 +10051,8 @@
         </is>
       </c>
       <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>Dr Mallen</t>
-        </is>
-      </c>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr">
         <is>
           <t>&lt;10</t>
@@ -10334,7 +10066,7 @@
       </c>
       <c r="AC78" t="inlineStr"/>
       <c r="AD78" t="inlineStr"/>
-      <c r="AE78" t="b">
+      <c r="AE78" t="n">
         <v>0</v>
       </c>
       <c r="AF78" t="inlineStr"/>
@@ -10446,11 +10178,7 @@
         </is>
       </c>
       <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Dr Roma</t>
-        </is>
-      </c>
+      <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr">
         <is>
@@ -10465,7 +10193,7 @@
       </c>
       <c r="AC79" t="inlineStr"/>
       <c r="AD79" t="inlineStr"/>
-      <c r="AE79" t="b">
+      <c r="AE79" t="n">
         <v>0</v>
       </c>
       <c r="AF79" t="inlineStr"/>
@@ -10579,14 +10307,10 @@
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Dr Roma</t>
-        </is>
-      </c>
+          <t>Dr. Madalitso</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
         <v>60</v>
       </c>
@@ -10598,7 +10322,7 @@
       </c>
       <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="b">
+      <c r="AE80" t="n">
         <v>0</v>
       </c>
       <c r="AF80" t="inlineStr"/>
@@ -10712,7 +10436,7 @@
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
+          <t>Dr. Madalitso</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr"/>
@@ -10727,7 +10451,7 @@
       </c>
       <c r="AC81" t="inlineStr"/>
       <c r="AD81" t="inlineStr"/>
-      <c r="AE81" t="b">
+      <c r="AE81" t="n">
         <v>0</v>
       </c>
       <c r="AF81" t="inlineStr"/>
@@ -10839,11 +10563,7 @@
         </is>
       </c>
       <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Dr Mallen</t>
-        </is>
-      </c>
+      <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr">
         <is>
@@ -10862,7 +10582,7 @@
         </is>
       </c>
       <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="b">
+      <c r="AE82" t="n">
         <v>0</v>
       </c>
       <c r="AF82" t="inlineStr"/>
@@ -10974,11 +10694,7 @@
         </is>
       </c>
       <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Dr Mallen</t>
-        </is>
-      </c>
+      <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr">
         <is>
@@ -10993,7 +10709,7 @@
       </c>
       <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr"/>
-      <c r="AE83" t="b">
+      <c r="AE83" t="n">
         <v>0</v>
       </c>
       <c r="AF83" t="inlineStr"/>
@@ -11105,11 +10821,7 @@
         </is>
       </c>
       <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Dr Mallen</t>
-        </is>
-      </c>
+      <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr">
         <is>
@@ -11124,7 +10836,7 @@
       </c>
       <c r="AC84" t="inlineStr"/>
       <c r="AD84" t="inlineStr"/>
-      <c r="AE84" t="b">
+      <c r="AE84" t="n">
         <v>1</v>
       </c>
       <c r="AF84" t="inlineStr">
@@ -11263,7 +10975,7 @@
       </c>
       <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="inlineStr"/>
-      <c r="AE85" t="b">
+      <c r="AE85" t="n">
         <v>0</v>
       </c>
       <c r="AF85" t="inlineStr"/>
@@ -11375,16 +11087,8 @@
         </is>
       </c>
       <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Dr Roma</t>
-        </is>
-      </c>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
         <v>55</v>
       </c>
@@ -11396,7 +11100,7 @@
       </c>
       <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="inlineStr"/>
-      <c r="AE86" t="b">
+      <c r="AE86" t="n">
         <v>0</v>
       </c>
       <c r="AF86" t="inlineStr"/>
@@ -11508,11 +11212,7 @@
         </is>
       </c>
       <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Visiting Resident</t>
-        </is>
-      </c>
+      <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr">
         <is>
@@ -11523,7 +11223,7 @@
         <v>268</v>
       </c>
       <c r="AB87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
@@ -11531,7 +11231,7 @@
         </is>
       </c>
       <c r="AD87" t="inlineStr"/>
-      <c r="AE87" t="b">
+      <c r="AE87" t="n">
         <v>0</v>
       </c>
       <c r="AF87" t="inlineStr"/>
@@ -11643,14 +11343,10 @@
         </is>
       </c>
       <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
+          <t>Dr. Madalitso</t>
         </is>
       </c>
       <c r="Z88" t="n">
@@ -11664,7 +11360,7 @@
       </c>
       <c r="AC88" t="inlineStr"/>
       <c r="AD88" t="inlineStr"/>
-      <c r="AE88" t="b">
+      <c r="AE88" t="n">
         <v>0</v>
       </c>
       <c r="AF88" t="inlineStr"/>
@@ -11776,11 +11472,7 @@
         </is>
       </c>
       <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Visiting Resident</t>
-        </is>
-      </c>
+      <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
         <v>75</v>
@@ -11793,7 +11485,7 @@
       </c>
       <c r="AC89" t="inlineStr"/>
       <c r="AD89" t="inlineStr"/>
-      <c r="AE89" t="b">
+      <c r="AE89" t="n">
         <v>0</v>
       </c>
       <c r="AF89" t="inlineStr"/>
@@ -11905,11 +11597,7 @@
         </is>
       </c>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Visiting Resident</t>
-        </is>
-      </c>
+      <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
         <v>90</v>
@@ -11922,7 +11610,7 @@
       </c>
       <c r="AC90" t="inlineStr"/>
       <c r="AD90" t="inlineStr"/>
-      <c r="AE90" t="b">
+      <c r="AE90" t="n">
         <v>0</v>
       </c>
       <c r="AF90" t="inlineStr"/>
@@ -12026,11 +11714,7 @@
         </is>
       </c>
       <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Visiting Resident</t>
-        </is>
-      </c>
+      <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="n">
         <v>50</v>
@@ -12043,7 +11727,7 @@
       </c>
       <c r="AC91" t="inlineStr"/>
       <c r="AD91" t="inlineStr"/>
-      <c r="AE91" t="b">
+      <c r="AE91" t="n">
         <v>0</v>
       </c>
       <c r="AF91" t="inlineStr"/>
@@ -12155,11 +11839,7 @@
         </is>
       </c>
       <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Visiting Resident</t>
-        </is>
-      </c>
+      <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr">
         <is>
@@ -12174,7 +11854,7 @@
       </c>
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
-      <c r="AE92" t="b">
+      <c r="AE92" t="n">
         <v>0</v>
       </c>
       <c r="AF92" t="inlineStr"/>
@@ -12286,11 +11966,7 @@
         </is>
       </c>
       <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="n">
         <v>50</v>
@@ -12307,7 +11983,7 @@
         </is>
       </c>
       <c r="AD93" t="inlineStr"/>
-      <c r="AE93" t="b">
+      <c r="AE93" t="n">
         <v>0</v>
       </c>
       <c r="AF93" t="inlineStr"/>
@@ -12419,11 +12095,7 @@
         </is>
       </c>
       <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="n">
         <v>90</v>
@@ -12436,7 +12108,7 @@
       </c>
       <c r="AC94" t="inlineStr"/>
       <c r="AD94" t="inlineStr"/>
-      <c r="AE94" t="b">
+      <c r="AE94" t="n">
         <v>0</v>
       </c>
       <c r="AF94" t="inlineStr"/>
@@ -12548,11 +12220,7 @@
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="n">
         <v>90</v>
@@ -12565,7 +12233,7 @@
       </c>
       <c r="AC95" t="inlineStr"/>
       <c r="AD95" t="inlineStr"/>
-      <c r="AE95" t="b">
+      <c r="AE95" t="n">
         <v>0</v>
       </c>
       <c r="AF95" t="inlineStr"/>
@@ -12681,11 +12349,7 @@
           <t>Dr Vaylann</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Dr Caleb</t>
-        </is>
-      </c>
+      <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="n">
         <v>30</v>
@@ -12698,7 +12362,7 @@
       </c>
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr"/>
-      <c r="AE96" t="b">
+      <c r="AE96" t="n">
         <v>1</v>
       </c>
       <c r="AF96" t="inlineStr">
@@ -12822,11 +12486,7 @@
           <t>Dr Vaylann</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
+      <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr">
         <is>
@@ -12841,7 +12501,7 @@
       </c>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
-      <c r="AE97" t="b">
+      <c r="AE97" t="n">
         <v>0</v>
       </c>
       <c r="AF97" t="inlineStr"/>
@@ -12953,11 +12613,7 @@
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="n">
         <v>50</v>
@@ -12970,7 +12626,7 @@
       </c>
       <c r="AC98" t="inlineStr"/>
       <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="b">
+      <c r="AE98" t="n">
         <v>0</v>
       </c>
       <c r="AF98" t="inlineStr"/>
@@ -13074,14 +12730,10 @@
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Dr Mallen</t>
-        </is>
-      </c>
+          <t>Dr. Madalitso</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="n">
         <v>50</v>
       </c>
@@ -13093,7 +12745,7 @@
       </c>
       <c r="AC99" t="inlineStr"/>
       <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="b">
+      <c r="AE99" t="n">
         <v>0</v>
       </c>
       <c r="AF99" t="inlineStr"/>
@@ -13207,11 +12859,7 @@
           <t>Dr Stuebing</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Dr Roma</t>
-        </is>
-      </c>
+      <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr">
         <is>
@@ -13226,7 +12874,7 @@
       </c>
       <c r="AC100" t="inlineStr"/>
       <c r="AD100" t="inlineStr"/>
-      <c r="AE100" t="b">
+      <c r="AE100" t="n">
         <v>0</v>
       </c>
       <c r="AF100" t="inlineStr"/>
@@ -13338,11 +12986,7 @@
         </is>
       </c>
       <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Dr Mallen</t>
-        </is>
-      </c>
+      <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr">
         <is>
@@ -13357,7 +13001,7 @@
       </c>
       <c r="AC101" t="inlineStr"/>
       <c r="AD101" t="inlineStr"/>
-      <c r="AE101" t="b">
+      <c r="AE101" t="n">
         <v>0</v>
       </c>
       <c r="AF101" t="inlineStr"/>
@@ -13455,16 +13099,8 @@
         </is>
       </c>
       <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Dr Wongani</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="n">
         <v>60</v>
       </c>
@@ -13476,7 +13112,7 @@
       </c>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr"/>
-      <c r="AE102" t="b">
+      <c r="AE102" t="n">
         <v>0</v>
       </c>
       <c r="AF102" t="inlineStr"/>
@@ -13590,14 +13226,10 @@
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>Dr Mallen</t>
-        </is>
-      </c>
+          <t>Dr. Madalitso</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="n">
         <v>50</v>
       </c>
@@ -13609,7 +13241,7 @@
       </c>
       <c r="AC103" t="inlineStr"/>
       <c r="AD103" t="inlineStr"/>
-      <c r="AE103" t="b">
+      <c r="AE103" t="n">
         <v>0</v>
       </c>
       <c r="AF103" t="inlineStr"/>
@@ -13723,14 +13355,10 @@
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Dr Roma</t>
-        </is>
-      </c>
+          <t>Dr. Madalitso</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="n">
         <v>60</v>
       </c>
@@ -13742,7 +13370,7 @@
       </c>
       <c r="AC104" t="inlineStr"/>
       <c r="AD104" t="inlineStr"/>
-      <c r="AE104" t="b">
+      <c r="AE104" t="n">
         <v>0</v>
       </c>
       <c r="AF104" t="inlineStr"/>
@@ -13854,14 +13482,10 @@
         </is>
       </c>
       <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Dr Jonathan</t>
-        </is>
-      </c>
+      <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>Dr Mada</t>
+          <t>Dr. Madalitso</t>
         </is>
       </c>
       <c r="Z105" t="n">
@@ -13875,7 +13499,7 @@
       </c>
       <c r="AC105" t="inlineStr"/>
       <c r="AD105" t="inlineStr"/>
-      <c r="AE105" t="b">
+      <c r="AE105" t="n">
         <v>0</v>
       </c>
       <c r="AF105" t="inlineStr"/>
